--- a/artfynd/A 12622-2026 artfynd.xlsx
+++ b/artfynd/A 12622-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY43"/>
+  <dimension ref="A1:AY45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132569084</v>
+        <v>132569105</v>
       </c>
       <c r="B2" t="n">
-        <v>80438</v>
+        <v>89354</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,26 +686,30 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>510</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -713,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>505125</v>
+        <v>505140</v>
       </c>
       <c r="R2" t="n">
-        <v>7117873</v>
+        <v>7117793</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +755,11 @@
           <t>2026-04-16</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar i en gammal granlåga.</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -766,24 +775,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Naturskogsartad grandominerad skog.</t>
+        </is>
+      </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -801,10 +815,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132569105</v>
+        <v>132614832</v>
       </c>
       <c r="B3" t="n">
-        <v>89300</v>
+        <v>89354</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -830,23 +844,16 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Nordväst om Bävertjärnberget, Jmt</t>
+          <t>Bävertjärnberget, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>505140</v>
+        <v>505049</v>
       </c>
       <c r="R3" t="n">
-        <v>7117793</v>
+        <v>7117892</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -881,70 +888,34 @@
           <t>2026-04-16</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar i en gammal granlåga.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Naturskogsartad grandominerad skog.</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132569085</v>
+        <v>132614833</v>
       </c>
       <c r="B4" t="n">
-        <v>80438</v>
+        <v>89354</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -952,37 +923,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>510</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Nordväst om Bävertjärnberget, Jmt</t>
+          <t>Bävertjärnberget, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>505135</v>
+        <v>505156</v>
       </c>
       <c r="R4" t="n">
-        <v>7118023</v>
+        <v>7118050</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1017,65 +985,34 @@
           <t>2026-04-16</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På en gammal sälg.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132569090</v>
+        <v>132569092</v>
       </c>
       <c r="B5" t="n">
-        <v>57136</v>
+        <v>91970</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1083,29 +1020,28 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102612</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1115,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>505163</v>
+        <v>505154</v>
       </c>
       <c r="R5" t="n">
-        <v>7117859</v>
+        <v>7117980</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1153,17 +1089,13 @@
           <t>2026-04-16</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Färsk spillning ovanpå snötäcket.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1172,9 +1104,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Ställvis flerskiktad gammal grandominerad skog med inslag av björk och sälg.</t>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1192,10 +1139,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132569104</v>
+        <v>132614826</v>
       </c>
       <c r="B6" t="n">
-        <v>79333</v>
+        <v>91970</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1203,37 +1150,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Nordväst om Bävertjärnberget, Jmt</t>
+          <t>Bävertjärnberget, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>505143</v>
+        <v>505198</v>
       </c>
       <c r="R6" t="n">
-        <v>7118040</v>
+        <v>7117708</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1268,65 +1212,34 @@
           <t>2026-04-16</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132569095</v>
+        <v>132614827</v>
       </c>
       <c r="B7" t="n">
-        <v>79333</v>
+        <v>91970</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1334,37 +1247,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Nordväst om Bävertjärnberget, Jmt</t>
+          <t>Bävertjärnberget, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>505186</v>
+        <v>505220</v>
       </c>
       <c r="R7" t="n">
-        <v>7117846</v>
+        <v>7117740</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1399,120 +1309,69 @@
           <t>2026-04-16</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132569088</v>
+        <v>132614828</v>
       </c>
       <c r="B8" t="n">
-        <v>58332</v>
+        <v>91970</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103015</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Nordväst om Bävertjärnberget, Jmt</t>
+          <t>Bävertjärnberget, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>505098</v>
+        <v>505217</v>
       </c>
       <c r="R8" t="n">
-        <v>7117979</v>
+        <v>7117743</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1556,35 +1415,25 @@
       <c r="AG8" t="b">
         <v>0</v>
       </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Ställvis flerskiktad gammal grandominerad skog med inslag av björk och sälg.</t>
-        </is>
-      </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132569077</v>
+        <v>132614830</v>
       </c>
       <c r="B9" t="n">
-        <v>80439</v>
+        <v>91970</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1592,37 +1441,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Nordväst om Bävertjärnberget, Jmt</t>
+          <t>Bävertjärnberget, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>505121</v>
+        <v>504969</v>
       </c>
       <c r="R9" t="n">
-        <v>7117940</v>
+        <v>7118078</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1663,97 +1509,63 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Ställvis flerskiktad gammal grandominerad skog med inslag av björk och sälg.</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132569098</v>
+        <v>132614834</v>
       </c>
       <c r="B10" t="n">
-        <v>79333</v>
+        <v>92647</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1339</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Nordväst om Bävertjärnberget, Jmt</t>
+          <t>Bävertjärnberget, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>505218</v>
+        <v>505168</v>
       </c>
       <c r="R10" t="n">
-        <v>7117716</v>
+        <v>7117694</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1788,65 +1600,34 @@
           <t>2026-04-16</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På en grov gammal gran.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132569078</v>
+        <v>132569077</v>
       </c>
       <c r="B11" t="n">
-        <v>80439</v>
+        <v>80489</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1881,10 +1662,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>505192</v>
+        <v>505121</v>
       </c>
       <c r="R11" t="n">
-        <v>7117756</v>
+        <v>7117940</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1974,10 +1755,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132569103</v>
+        <v>132569078</v>
       </c>
       <c r="B12" t="n">
-        <v>79333</v>
+        <v>80489</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1985,21 +1766,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -2012,10 +1793,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>505114</v>
+        <v>505192</v>
       </c>
       <c r="R12" t="n">
-        <v>7117982</v>
+        <v>7117756</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2050,11 +1831,6 @@
           <t>2026-04-16</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På flera stående döda granar.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2070,24 +1846,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Ställvis flerskiktad gammal grandominerad skog med inslag av björk och sälg.</t>
+        </is>
+      </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2105,10 +1886,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132569099</v>
+        <v>132569080</v>
       </c>
       <c r="B13" t="n">
-        <v>79333</v>
+        <v>80489</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2116,21 +1897,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2143,10 +1924,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>505142</v>
+        <v>505126</v>
       </c>
       <c r="R13" t="n">
-        <v>7117802</v>
+        <v>7117873</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2181,11 +1962,6 @@
           <t>2026-04-16</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På en stående död gran.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2201,24 +1977,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Ställvis flerskiktad gammal grandominerad skog med inslag av björk och sälg.</t>
+        </is>
+      </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2236,10 +2017,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132569100</v>
+        <v>132569081</v>
       </c>
       <c r="B14" t="n">
-        <v>79333</v>
+        <v>80489</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2247,21 +2028,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2274,10 +2055,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>505120</v>
+        <v>505103</v>
       </c>
       <c r="R14" t="n">
-        <v>7117829</v>
+        <v>7117891</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2327,24 +2108,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Ställvis flerskiktad gammal grandominerad skog med inslag av björk och sälg.</t>
+        </is>
+      </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2362,53 +2148,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132569089</v>
+        <v>132614815</v>
       </c>
       <c r="B15" t="n">
-        <v>57136</v>
+        <v>92199</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102612</v>
+        <v>3298</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Nordväst om Bävertjärnberget, Jmt</t>
+          <t>Bävertjärnberget, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>505148</v>
+        <v>505047</v>
       </c>
       <c r="R15" t="n">
-        <v>7118008</v>
+        <v>7117865</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2443,11 +2221,6 @@
           <t>2026-04-16</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Färsk spillning ovanpå snötäcket.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2456,74 +2229,61 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>Ställvis flerskiktad och luckig gammal grandominerad skog med inslag av björk och sälg.</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132569096</v>
+        <v>132614816</v>
       </c>
       <c r="B16" t="n">
-        <v>79333</v>
+        <v>92199</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Nordväst om Bävertjärnberget, Jmt</t>
+          <t>Bävertjärnberget, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>505226</v>
+        <v>505117</v>
       </c>
       <c r="R16" t="n">
-        <v>7117776</v>
+        <v>7118060</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2564,82 +2324,55 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132569082</v>
+        <v>132569094</v>
       </c>
       <c r="B17" t="n">
-        <v>97995</v>
+        <v>79373</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2647,10 +2380,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>505118</v>
+        <v>505141</v>
       </c>
       <c r="R17" t="n">
-        <v>7117908</v>
+        <v>7117884</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2685,6 +2418,11 @@
           <t>2026-04-16</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Relativt rikligt med garnlav på en gran.</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2698,6 +2436,26 @@
       <c r="AH17" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2715,14 +2473,14 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132569101</v>
+        <v>132569095</v>
       </c>
       <c r="B18" t="n">
-        <v>79333</v>
+        <v>79373</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2753,10 +2511,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>505109</v>
+        <v>505186</v>
       </c>
       <c r="R18" t="n">
-        <v>7117890</v>
+        <v>7117846</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2793,7 +2551,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På en gammal gran.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2846,32 +2604,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132569081</v>
+        <v>132569096</v>
       </c>
       <c r="B19" t="n">
-        <v>80439</v>
+        <v>79373</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2884,10 +2642,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>505103</v>
+        <v>505226</v>
       </c>
       <c r="R19" t="n">
-        <v>7117891</v>
+        <v>7117776</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2937,29 +2695,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>Ställvis flerskiktad gammal grandominerad skog med inslag av björk och sälg.</t>
-        </is>
-      </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2980,11 +2733,11 @@
         <v>132569097</v>
       </c>
       <c r="B20" t="n">
-        <v>79333</v>
+        <v>79373</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -3108,14 +2861,14 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132569102</v>
+        <v>132569098</v>
       </c>
       <c r="B21" t="n">
-        <v>79333</v>
+        <v>79373</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -3146,10 +2899,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>505081</v>
+        <v>505218</v>
       </c>
       <c r="R21" t="n">
-        <v>7117938</v>
+        <v>7117716</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3186,7 +2939,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>På en grov gammal gran.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3239,27 +2992,27 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132569106</v>
+        <v>132569099</v>
       </c>
       <c r="B22" t="n">
-        <v>80473</v>
+        <v>79373</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3269,11 +3022,7 @@
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3281,10 +3030,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>505124</v>
+        <v>505142</v>
       </c>
       <c r="R22" t="n">
-        <v>7117873</v>
+        <v>7117802</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3321,7 +3070,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Sannolikt apothecier på flertalet bålar.</t>
+          <t>På en stående död gran.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3339,29 +3088,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>Äldre naturskogsartad grandominerad skog.</t>
-        </is>
-      </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3379,32 +3123,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132569083</v>
+        <v>132569100</v>
       </c>
       <c r="B23" t="n">
-        <v>80466</v>
+        <v>79373</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3417,10 +3161,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>505166</v>
+        <v>505120</v>
       </c>
       <c r="R23" t="n">
-        <v>7117864</v>
+        <v>7117829</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3468,6 +3212,26 @@
       <c r="AH23" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3485,32 +3249,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132569080</v>
+        <v>132569101</v>
       </c>
       <c r="B24" t="n">
-        <v>80439</v>
+        <v>79373</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3523,10 +3287,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>505126</v>
+        <v>505109</v>
       </c>
       <c r="R24" t="n">
-        <v>7117873</v>
+        <v>7117890</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3561,6 +3325,11 @@
           <t>2026-04-16</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>På en gammal gran.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3576,29 +3345,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>Ställvis flerskiktad gammal grandominerad skog med inslag av björk och sälg.</t>
-        </is>
-      </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3616,14 +3380,14 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132569094</v>
+        <v>132569102</v>
       </c>
       <c r="B25" t="n">
-        <v>79333</v>
+        <v>79373</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -3654,10 +3418,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>505141</v>
+        <v>505081</v>
       </c>
       <c r="R25" t="n">
-        <v>7117884</v>
+        <v>7117938</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3694,7 +3458,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Relativt rikligt med garnlav på en gran.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3747,45 +3511,48 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132614826</v>
+        <v>132569103</v>
       </c>
       <c r="B26" t="n">
-        <v>91914</v>
+        <v>79373</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Bävertjärnberget, Jmt</t>
+          <t>Nordväst om Bävertjärnberget, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>505198</v>
+        <v>505114</v>
       </c>
       <c r="R26" t="n">
-        <v>7117708</v>
+        <v>7117982</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3820,69 +3587,103 @@
           <t>2026-04-16</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>På flera stående döda granar.</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132614832</v>
+        <v>132569104</v>
       </c>
       <c r="B27" t="n">
-        <v>89300</v>
+        <v>79373</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Bävertjärnberget, Jmt</t>
+          <t>Nordväst om Bävertjärnberget, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>505049</v>
+        <v>505143</v>
       </c>
       <c r="R27" t="n">
-        <v>7117892</v>
+        <v>7118040</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3917,56 +3718,87 @@
           <t>2026-04-16</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132614834</v>
+        <v>132614831</v>
       </c>
       <c r="B28" t="n">
-        <v>92573</v>
+        <v>79373</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1339</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3976,10 +3808,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>505168</v>
+        <v>505273</v>
       </c>
       <c r="R28" t="n">
-        <v>7117694</v>
+        <v>7117573</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4038,10 +3870,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132614830</v>
+        <v>132569084</v>
       </c>
       <c r="B29" t="n">
-        <v>91914</v>
+        <v>80488</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4049,34 +3881,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Bävertjärnberget, Jmt</t>
+          <t>Nordväst om Bävertjärnberget, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>504969</v>
+        <v>505125</v>
       </c>
       <c r="R29" t="n">
-        <v>7118078</v>
+        <v>7117873</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4117,63 +3952,92 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132614815</v>
+        <v>132569085</v>
       </c>
       <c r="B30" t="n">
-        <v>92641</v>
+        <v>80488</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3298</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Bävertjärnberget, Jmt</t>
+          <t>Nordväst om Bävertjärnberget, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>505047</v>
+        <v>505135</v>
       </c>
       <c r="R30" t="n">
-        <v>7117865</v>
+        <v>7118023</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4208,69 +4072,103 @@
           <t>2026-04-16</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På en gammal sälg.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132614831</v>
+        <v>132569083</v>
       </c>
       <c r="B31" t="n">
-        <v>79333</v>
+        <v>80492</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Bävertjärnberget, Jmt</t>
+          <t>Nordväst om Bävertjärnberget, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>505273</v>
+        <v>505166</v>
       </c>
       <c r="R31" t="n">
-        <v>7117573</v>
+        <v>7117864</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4311,63 +4209,76 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132614828</v>
+        <v>132569106</v>
       </c>
       <c r="B32" t="n">
-        <v>91914</v>
+        <v>80499</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1108</v>
+        <v>6463</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Bävertjärnberget, Jmt</t>
+          <t>Nordväst om Bävertjärnberget, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>505217</v>
+        <v>505124</v>
       </c>
       <c r="R32" t="n">
-        <v>7117743</v>
+        <v>7117873</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4402,34 +4313,70 @@
           <t>2026-04-16</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Sannolikt apothecier på flertalet bålar.</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>Äldre naturskogsartad grandominerad skog.</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132614827</v>
+        <v>132569073</v>
       </c>
       <c r="B33" t="n">
-        <v>91914</v>
+        <v>57975</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4437,34 +4384,42 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Bävertjärnberget, Jmt</t>
+          <t>Nordväst om Bävertjärnberget, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>505220</v>
+        <v>505235</v>
       </c>
       <c r="R33" t="n">
-        <v>7117740</v>
+        <v>7117722</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4499,6 +4454,11 @@
           <t>2026-04-16</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en stående död gran.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4507,26 +4467,56 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>Ställvis flerskiktad gammal grandominerad skog med inslag av björk och sälg.</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132614833</v>
+        <v>132569074</v>
       </c>
       <c r="B34" t="n">
-        <v>89300</v>
+        <v>57975</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4534,34 +4524,42 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Bävertjärnberget, Jmt</t>
+          <t>Nordväst om Bävertjärnberget, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>505156</v>
+        <v>505146</v>
       </c>
       <c r="R34" t="n">
-        <v>7118050</v>
+        <v>7118037</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4596,6 +4594,11 @@
           <t>2026-04-16</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska och äldre, på en gran vid en bäck. De färska ringhacken bedöms skapade inom 5 år bakåt. Intill granen med ringhack finns en barkskalad stående död gran med sannolika födosökspår efter tretåig hackspett. Kring fyndplatsen finns en volym stående död ved av gran som indikerar högt livsmiljövärde för tretåig hackspett.</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4604,48 +4607,78 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>Ställvis flerskiktad gammal grandominerad skog med inslag av björk och sälg. Här finns gott om stående och liggande död ved.</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132614816</v>
+        <v>132614817</v>
       </c>
       <c r="B35" t="n">
-        <v>92641</v>
+        <v>57975</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4655,10 +4688,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>505117</v>
+        <v>505009</v>
       </c>
       <c r="R35" t="n">
-        <v>7118060</v>
+        <v>7117964</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4691,6 +4724,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4717,7 +4755,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132614823</v>
+        <v>132614818</v>
       </c>
       <c r="B36" t="n">
         <v>57975</v>
@@ -4752,10 +4790,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>505270</v>
+        <v>505149</v>
       </c>
       <c r="R36" t="n">
-        <v>7117534</v>
+        <v>7117788</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4792,7 +4830,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Bohål ca 3,5m upp i död gran</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4921,7 +4959,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132614821</v>
+        <v>132614820</v>
       </c>
       <c r="B38" t="n">
         <v>57975</v>
@@ -4956,10 +4994,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>505275</v>
+        <v>505256</v>
       </c>
       <c r="R38" t="n">
-        <v>7117570</v>
+        <v>7117713</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4996,7 +5034,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5023,7 +5061,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132614818</v>
+        <v>132614821</v>
       </c>
       <c r="B39" t="n">
         <v>57975</v>
@@ -5058,10 +5096,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>505149</v>
+        <v>505275</v>
       </c>
       <c r="R39" t="n">
-        <v>7117788</v>
+        <v>7117570</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5098,7 +5136,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Bohål ca 3,5m upp i död gran</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5125,7 +5163,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132569074</v>
+        <v>132614823</v>
       </c>
       <c r="B40" t="n">
         <v>57975</v>
@@ -5154,24 +5192,16 @@
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Nordväst om Bävertjärnberget, Jmt</t>
+          <t>Bävertjärnberget, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>505146</v>
+        <v>505270</v>
       </c>
       <c r="R40" t="n">
-        <v>7118037</v>
+        <v>7117534</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5208,7 +5238,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska och äldre, på en gran vid en bäck. De färska ringhacken bedöms skapade inom 5 år bakåt. Intill granen med ringhack finns en barkskalad stående död gran med sannolika födosökspår efter tretåig hackspett. Kring fyndplatsen finns en volym stående död ved av gran som indikerar högt livsmiljövärde för tretåig hackspett.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5219,73 +5249,43 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>Ställvis flerskiktad gammal grandominerad skog med inslag av björk och sälg. Här finns gott om stående och liggande död ved.</t>
-        </is>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132569073</v>
+        <v>132569089</v>
       </c>
       <c r="B41" t="n">
-        <v>57975</v>
+        <v>57153</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -5298,7 +5298,7 @@
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
@@ -5308,10 +5308,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>505235</v>
+        <v>505148</v>
       </c>
       <c r="R41" t="n">
-        <v>7117722</v>
+        <v>7118008</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en stående död gran.</t>
+          <t>Färsk spillning ovanpå snötäcket.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5367,27 +5367,7 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>Ställvis flerskiktad gammal grandominerad skog med inslag av björk och sälg.</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Ställvis flerskiktad och luckig gammal grandominerad skog med inslag av björk och sälg.</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5405,27 +5385,27 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132614817</v>
+        <v>132569090</v>
       </c>
       <c r="B42" t="n">
-        <v>57975</v>
+        <v>57153</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -5434,16 +5414,24 @@
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Bävertjärnberget, Jmt</t>
+          <t>Nordväst om Bävertjärnberget, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>505009</v>
+        <v>505163</v>
       </c>
       <c r="R42" t="n">
-        <v>7117964</v>
+        <v>7117859</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5480,7 +5468,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Färsk spillning ovanpå snötäcket.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5491,43 +5479,53 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>Ställvis flerskiktad gammal grandominerad skog med inslag av björk och sälg.</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132614820</v>
+        <v>132569088</v>
       </c>
       <c r="B43" t="n">
-        <v>57975</v>
+        <v>58349</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -5535,17 +5533,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Bävertjärnberget, Jmt</t>
+          <t>Nordväst om Bävertjärnberget, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>505256</v>
+        <v>505098</v>
       </c>
       <c r="R43" t="n">
-        <v>7117713</v>
+        <v>7117979</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5580,11 +5598,6 @@
           <t>2026-04-16</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5593,19 +5606,243 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>Ställvis flerskiktad gammal grandominerad skog med inslag av björk och sälg.</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>132569087</v>
+      </c>
+      <c r="B44" t="n">
+        <v>111153</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Nordväst om Bävertjärnberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>505157</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7117774</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>132569082</v>
+      </c>
+      <c r="B45" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Nordväst om Bävertjärnberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>505118</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7117908</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 12622-2026 artfynd.xlsx
+++ b/artfynd/A 12622-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY39"/>
+  <dimension ref="A1:AZ39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132614833</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -899,6 +909,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132569092</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -996,6 +1011,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132614826</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1093,6 +1113,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132614827</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1190,6 +1215,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132614828</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1287,6 +1317,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132614830</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1418,6 +1453,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132569077</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1549,6 +1589,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132569078</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1680,6 +1725,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132569080</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1811,6 +1861,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132569081</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1908,6 +1963,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132614816</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2039,6 +2099,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132569094</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2170,6 +2235,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132569095</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2296,6 +2366,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132569096</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2427,6 +2502,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132569097</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2558,6 +2638,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132569098</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2684,6 +2769,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132569100</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2815,6 +2905,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132569101</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2946,6 +3041,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132569102</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3077,6 +3177,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132569103</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3208,6 +3313,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132569104</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3305,6 +3415,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132614831</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3431,6 +3546,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132569084</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3562,6 +3682,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132569085</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3668,6 +3793,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132569083</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3808,6 +3938,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132569106</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3948,6 +4083,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132569073</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4088,6 +4228,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132569074</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4190,6 +4335,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132614817</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4292,6 +4442,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132614819</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4394,6 +4549,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132614820</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4496,6 +4656,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132614821</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4598,6 +4763,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132614823</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4718,6 +4888,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132569089</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4838,6 +5013,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132569090</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4965,6 +5145,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132569088</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5072,6 +5257,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132569087</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5179,8 +5369,53 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132569082</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>